--- a/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP254"/>
+  <dimension ref="A1:BP255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ19" t="n">
         <v>2.08</v>
@@ -5928,7 +5928,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR25" t="n">
         <v>1.71</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.08</v>
@@ -11378,7 +11378,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR50" t="n">
         <v>0.91</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.92</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.85</v>
@@ -18136,7 +18136,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR81" t="n">
         <v>1.64</v>
@@ -18351,7 +18351,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.25</v>
@@ -22496,7 +22496,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR101" t="n">
         <v>1.54</v>
@@ -24673,7 +24673,7 @@
         <v>0</v>
       </c>
       <c r="AP111" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ111" t="n">
         <v>0.6899999999999999</v>
@@ -28161,7 +28161,7 @@
         <v>1.29</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.85</v>
@@ -28600,7 +28600,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR129" t="n">
         <v>1.08</v>
@@ -31434,7 +31434,7 @@
         <v>3</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR142" t="n">
         <v>2.27</v>
@@ -31867,7 +31867,7 @@
         <v>0.43</v>
       </c>
       <c r="AP144" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.38</v>
@@ -32742,7 +32742,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR148" t="n">
         <v>1.58</v>
@@ -36227,7 +36227,7 @@
         <v>2</v>
       </c>
       <c r="AP164" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.67</v>
@@ -37102,7 +37102,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR168" t="n">
         <v>1.19</v>
@@ -40154,7 +40154,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR182" t="n">
         <v>1.56</v>
@@ -40587,7 +40587,7 @@
         <v>1.33</v>
       </c>
       <c r="AP184" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.46</v>
@@ -46691,7 +46691,7 @@
         <v>1.2</v>
       </c>
       <c r="AP212" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.08</v>
@@ -47130,7 +47130,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR214" t="n">
         <v>1.27</v>
@@ -51705,7 +51705,7 @@
         <v>0.73</v>
       </c>
       <c r="AP235" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ235" t="n">
         <v>0.92</v>
@@ -51926,7 +51926,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR236" t="n">
         <v>1.68</v>
@@ -55926,6 +55926,224 @@
       </c>
       <c r="BP254" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>8200622</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>46081.70833333334</v>
+      </c>
+      <c r="F255" t="n">
+        <v>26</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" t="n">
+        <v>1</v>
+      </c>
+      <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R255" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S255" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T255" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U255" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V255" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W255" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X255" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO255" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP255" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ255" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT255" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AU255" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX255" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY255" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ255" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA255" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB255" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC255" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BE255" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF255" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG255" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI255" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ255" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK255" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL255" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM255" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BN255" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO255" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP255" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP255"/>
+  <dimension ref="A1:BP260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.85</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.08</v>
@@ -2004,7 +2004,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.46</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.62</v>
@@ -3312,7 +3312,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR13" t="n">
         <v>0.5</v>
@@ -4184,7 +4184,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.85</v>
@@ -5707,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR24" t="n">
         <v>1.65</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR27" t="n">
         <v>0.86</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.38</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.92</v>
@@ -7236,7 +7236,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR31" t="n">
         <v>1.28</v>
@@ -9849,7 +9849,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.08</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.85</v>
@@ -10285,10 +10285,10 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR45" t="n">
         <v>2.18</v>
@@ -10506,7 +10506,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR46" t="n">
         <v>1.19</v>
@@ -10724,7 +10724,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR47" t="n">
         <v>2.48</v>
@@ -10939,7 +10939,7 @@
         <v>3</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.92</v>
@@ -11160,7 +11160,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR49" t="n">
         <v>1.46</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.5</v>
@@ -11814,7 +11814,7 @@
         <v>3</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR52" t="n">
         <v>2.59</v>
@@ -13991,10 +13991,10 @@
         <v>0.5</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR62" t="n">
         <v>1.21</v>
@@ -15084,7 +15084,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR67" t="n">
         <v>1.6</v>
@@ -15299,10 +15299,10 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR68" t="n">
         <v>1.48</v>
@@ -15735,10 +15735,10 @@
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR70" t="n">
         <v>1.55</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.5</v>
@@ -16174,7 +16174,7 @@
         <v>2</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR72" t="n">
         <v>1.33</v>
@@ -16607,7 +16607,7 @@
         <v>0.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.6899999999999999</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.54</v>
@@ -18354,7 +18354,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR82" t="n">
         <v>0.95</v>
@@ -19226,7 +19226,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR86" t="n">
         <v>1.7</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.92</v>
@@ -20534,7 +20534,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR92" t="n">
         <v>1.75</v>
@@ -20749,7 +20749,7 @@
         <v>0.75</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.5</v>
@@ -21188,7 +21188,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR95" t="n">
         <v>1.63</v>
@@ -21403,7 +21403,7 @@
         <v>1</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.54</v>
@@ -21839,7 +21839,7 @@
         <v>2</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.92</v>
@@ -22060,7 +22060,7 @@
         <v>2</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR99" t="n">
         <v>1.24</v>
@@ -22493,7 +22493,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.31</v>
@@ -23150,7 +23150,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR104" t="n">
         <v>1.79</v>
@@ -23583,7 +23583,7 @@
         <v>0.4</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.6899999999999999</v>
@@ -23804,7 +23804,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR107" t="n">
         <v>1.15</v>
@@ -24022,7 +24022,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR108" t="n">
         <v>1.45</v>
@@ -24455,7 +24455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.38</v>
@@ -24676,7 +24676,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR111" t="n">
         <v>1.04</v>
@@ -24891,7 +24891,7 @@
         <v>0.4</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.08</v>
@@ -25109,7 +25109,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.62</v>
@@ -25330,7 +25330,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR114" t="n">
         <v>1.41</v>
@@ -26417,7 +26417,7 @@
         <v>1.4</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.46</v>
@@ -26638,7 +26638,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR120" t="n">
         <v>1.21</v>
@@ -27071,7 +27071,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.85</v>
@@ -27292,7 +27292,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR123" t="n">
         <v>1.44</v>
@@ -28379,7 +28379,7 @@
         <v>0.4</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.08</v>
@@ -28815,7 +28815,7 @@
         <v>2.17</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ130" t="n">
         <v>2.08</v>
@@ -29036,7 +29036,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -29472,7 +29472,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR133" t="n">
         <v>1.17</v>
@@ -30780,7 +30780,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR139" t="n">
         <v>1.41</v>
@@ -30995,7 +30995,7 @@
         <v>2</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ140" t="n">
         <v>2.08</v>
@@ -32088,7 +32088,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR145" t="n">
         <v>1.99</v>
@@ -32521,7 +32521,7 @@
         <v>1.86</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.92</v>
@@ -32957,7 +32957,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.08</v>
@@ -33175,10 +33175,10 @@
         <v>1.29</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR150" t="n">
         <v>1.47</v>
@@ -33611,10 +33611,10 @@
         <v>1.83</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR152" t="n">
         <v>2.38</v>
@@ -34704,7 +34704,7 @@
         <v>3</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR157" t="n">
         <v>2.24</v>
@@ -34922,7 +34922,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR158" t="n">
         <v>1.15</v>
@@ -36009,7 +36009,7 @@
         <v>0.5</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.38</v>
@@ -36230,7 +36230,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR164" t="n">
         <v>1.08</v>
@@ -36881,10 +36881,10 @@
         <v>1.25</v>
       </c>
       <c r="AP167" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR167" t="n">
         <v>2.39</v>
@@ -37099,7 +37099,7 @@
         <v>1.13</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.31</v>
@@ -37535,7 +37535,7 @@
         <v>1.11</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.85</v>
@@ -37753,10 +37753,10 @@
         <v>1.13</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR171" t="n">
         <v>1.78</v>
@@ -37974,7 +37974,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR172" t="n">
         <v>1.57</v>
@@ -38192,7 +38192,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR173" t="n">
         <v>1.81</v>
@@ -38843,7 +38843,7 @@
         <v>1.86</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.54</v>
@@ -39497,7 +39497,7 @@
         <v>1.5</v>
       </c>
       <c r="AP179" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.46</v>
@@ -41023,10 +41023,10 @@
         <v>0.22</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR186" t="n">
         <v>1.17</v>
@@ -41241,7 +41241,7 @@
         <v>0.38</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.33</v>
@@ -41680,7 +41680,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR189" t="n">
         <v>1.15</v>
@@ -41898,7 +41898,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR190" t="n">
         <v>1.43</v>
@@ -42331,7 +42331,7 @@
         <v>1.1</v>
       </c>
       <c r="AP192" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ192" t="n">
         <v>0.85</v>
@@ -42985,7 +42985,7 @@
         <v>2</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.54</v>
@@ -44075,10 +44075,10 @@
         <v>1.11</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR200" t="n">
         <v>1.65</v>
@@ -44514,7 +44514,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR202" t="n">
         <v>1.73</v>
@@ -44729,10 +44729,10 @@
         <v>1.67</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR203" t="n">
         <v>1.49</v>
@@ -45822,7 +45822,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR208" t="n">
         <v>1.57</v>
@@ -46255,10 +46255,10 @@
         <v>1</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR210" t="n">
         <v>1.16</v>
@@ -47345,7 +47345,7 @@
         <v>2</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.92</v>
@@ -47563,7 +47563,7 @@
         <v>0.91</v>
       </c>
       <c r="AP216" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.85</v>
@@ -47781,7 +47781,7 @@
         <v>0.6</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.6899999999999999</v>
@@ -48002,7 +48002,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR218" t="n">
         <v>1.15</v>
@@ -48438,7 +48438,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR220" t="n">
         <v>1.28</v>
@@ -48656,7 +48656,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ221" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR221" t="n">
         <v>1.33</v>
@@ -49310,7 +49310,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR224" t="n">
         <v>1.44</v>
@@ -50179,7 +50179,7 @@
         <v>2.18</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ228" t="n">
         <v>2.08</v>
@@ -50400,7 +50400,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR229" t="n">
         <v>1.7</v>
@@ -50615,10 +50615,10 @@
         <v>0.67</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ230" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR230" t="n">
         <v>1.56</v>
@@ -50836,7 +50836,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ231" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR231" t="n">
         <v>1.45</v>
@@ -51487,7 +51487,7 @@
         <v>1</v>
       </c>
       <c r="AP234" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.08</v>
@@ -52577,7 +52577,7 @@
         <v>2.08</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ239" t="n">
         <v>1.92</v>
@@ -53449,7 +53449,7 @@
         <v>0.83</v>
       </c>
       <c r="AP243" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.85</v>
@@ -53888,7 +53888,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR245" t="n">
         <v>1.91</v>
@@ -54106,7 +54106,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR246" t="n">
         <v>1.1</v>
@@ -56144,6 +56144,1096 @@
       </c>
       <c r="BP255" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>8200754</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>46082.41666666666</v>
+      </c>
+      <c r="F256" t="n">
+        <v>26</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" t="n">
+        <v>2</v>
+      </c>
+      <c r="L256" t="n">
+        <v>2</v>
+      </c>
+      <c r="M256" t="n">
+        <v>2</v>
+      </c>
+      <c r="N256" t="n">
+        <v>4</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>['42', '90']</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>['7', '57']</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R256" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S256" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T256" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U256" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V256" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="W256" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X256" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU256" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY256" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA256" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB256" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC256" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE256" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF256" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG256" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH256" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI256" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ256" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BK256" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL256" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM256" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BN256" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO256" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP256" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>8200755</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>46082.51041666666</v>
+      </c>
+      <c r="F257" t="n">
+        <v>26</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>1</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R257" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S257" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T257" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U257" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V257" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W257" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X257" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ257" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR257" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS257" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT257" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW257" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX257" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY257" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ257" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA257" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB257" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC257" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE257" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF257" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG257" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH257" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI257" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ257" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK257" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL257" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM257" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BN257" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO257" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP257" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>8200621</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>46082.60416666666</v>
+      </c>
+      <c r="F258" t="n">
+        <v>26</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>2</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>2</v>
+      </c>
+      <c r="L258" t="n">
+        <v>2</v>
+      </c>
+      <c r="M258" t="n">
+        <v>2</v>
+      </c>
+      <c r="N258" t="n">
+        <v>4</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>['16', '37']</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>['62', '85']</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R258" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S258" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T258" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U258" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V258" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W258" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X258" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO258" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ258" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR258" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS258" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT258" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV258" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW258" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX258" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY258" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ258" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA258" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB258" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC258" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE258" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF258" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BG258" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH258" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI258" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ258" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK258" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL258" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM258" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN258" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO258" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP258" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>8200708</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>46082.70833333334</v>
+      </c>
+      <c r="F259" t="n">
+        <v>26</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" t="n">
+        <v>2</v>
+      </c>
+      <c r="N259" t="n">
+        <v>3</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>['58', '70']</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R259" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S259" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T259" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U259" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V259" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W259" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X259" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ259" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU259" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV259" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY259" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA259" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB259" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC259" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE259" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF259" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BG259" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH259" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI259" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ259" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BK259" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL259" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM259" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BN259" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO259" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BP259" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>8200747</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>46083.70833333334</v>
+      </c>
+      <c r="F260" t="n">
+        <v>26</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" t="n">
+        <v>1</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0</v>
+      </c>
+      <c r="M260" t="n">
+        <v>1</v>
+      </c>
+      <c r="N260" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R260" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S260" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U260" t="n">
+        <v>3</v>
+      </c>
+      <c r="V260" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W260" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X260" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AU260" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX260" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY260" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ260" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA260" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB260" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC260" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE260" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF260" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG260" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH260" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BI260" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM260" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN260" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO260" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP260" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP260"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.92</v>
@@ -7890,7 +7890,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.77</v>
@@ -11596,7 +11596,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR51" t="n">
         <v>1.36</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.15</v>
@@ -15956,7 +15956,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR71" t="n">
         <v>1.35</v>
@@ -20752,7 +20752,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR93" t="n">
         <v>1.15</v>
@@ -22275,7 +22275,7 @@
         <v>1</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.62</v>
@@ -25984,7 +25984,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR117" t="n">
         <v>1.51</v>
@@ -26199,7 +26199,7 @@
         <v>2.4</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ118" t="n">
         <v>2.08</v>
@@ -30126,7 +30126,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR136" t="n">
         <v>1.95</v>
@@ -31213,7 +31213,7 @@
         <v>0.33</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.6899999999999999</v>
@@ -35140,7 +35140,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR159" t="n">
         <v>1.34</v>
@@ -35791,7 +35791,7 @@
         <v>1.57</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.46</v>
@@ -38189,7 +38189,7 @@
         <v>1</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.31</v>
@@ -39936,7 +39936,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR181" t="n">
         <v>1.3</v>
@@ -41459,7 +41459,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.38</v>
@@ -42770,7 +42770,7 @@
         <v>2</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR194" t="n">
         <v>1.46</v>
@@ -44511,7 +44511,7 @@
         <v>0.2</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.64</v>
@@ -45604,7 +45604,7 @@
         <v>3</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR207" t="n">
         <v>2.29</v>
@@ -51923,7 +51923,7 @@
         <v>1.27</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ236" t="n">
         <v>1.31</v>
@@ -53234,7 +53234,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ242" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR242" t="n">
         <v>1.5</v>
@@ -55411,7 +55411,7 @@
         <v>0.92</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ252" t="n">
         <v>0.92</v>
@@ -57234,6 +57234,224 @@
       </c>
       <c r="BP260" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>8200746</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>46085.625</v>
+      </c>
+      <c r="F261" t="n">
+        <v>23</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>1</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" t="n">
+        <v>3</v>
+      </c>
+      <c r="M261" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" t="n">
+        <v>3</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>['44', '50', '62']</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R261" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S261" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T261" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U261" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V261" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="W261" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X261" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ261" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU261" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX261" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY261" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA261" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB261" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC261" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE261" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF261" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG261" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH261" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BI261" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM261" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN261" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO261" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP261" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.31</v>
@@ -3745,7 +3745,7 @@
         <v>3</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.92</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.6899999999999999</v>
@@ -4402,7 +4402,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR18" t="n">
         <v>2.89</v>
@@ -4620,7 +4620,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.46</v>
@@ -6582,7 +6582,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR28" t="n">
         <v>2.14</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.54</v>
@@ -8108,7 +8108,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR35" t="n">
         <v>1.77</v>
@@ -8759,10 +8759,10 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR38" t="n">
         <v>1.4</v>
@@ -8977,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.46</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.85</v>
@@ -9634,7 +9634,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR42" t="n">
         <v>1.24</v>
@@ -12250,7 +12250,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR54" t="n">
         <v>1.43</v>
@@ -12683,10 +12683,10 @@
         <v>3</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ56" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR56" t="n">
         <v>0.84</v>
@@ -13340,7 +13340,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR59" t="n">
         <v>2</v>
@@ -13555,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.33</v>
@@ -14430,7 +14430,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ64" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR64" t="n">
         <v>1.74</v>
@@ -16171,7 +16171,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.31</v>
@@ -16828,7 +16828,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR75" t="n">
         <v>1.56</v>
@@ -18133,7 +18133,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.31</v>
@@ -18572,7 +18572,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR83" t="n">
         <v>1.42</v>
@@ -18790,7 +18790,7 @@
         <v>3</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR84" t="n">
         <v>2.45</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.08</v>
@@ -19877,7 +19877,7 @@
         <v>1.2</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.85</v>
@@ -20098,7 +20098,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ90" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR90" t="n">
         <v>1.1</v>
@@ -22057,7 +22057,7 @@
         <v>0.67</v>
       </c>
       <c r="AP99" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.77</v>
@@ -22714,7 +22714,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR102" t="n">
         <v>1</v>
@@ -23801,7 +23801,7 @@
         <v>1.25</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.77</v>
@@ -24458,7 +24458,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR110" t="n">
         <v>1.64</v>
@@ -26202,7 +26202,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ118" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR118" t="n">
         <v>1.74</v>
@@ -26853,7 +26853,7 @@
         <v>1.67</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.92</v>
@@ -27725,7 +27725,7 @@
         <v>0.5</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.08</v>
@@ -27946,7 +27946,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR126" t="n">
         <v>2.01</v>
@@ -28382,7 +28382,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR128" t="n">
         <v>1.67</v>
@@ -28818,7 +28818,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ130" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR130" t="n">
         <v>1.59</v>
@@ -29905,7 +29905,7 @@
         <v>0.67</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.92</v>
@@ -30777,7 +30777,7 @@
         <v>1</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.23</v>
@@ -30998,7 +30998,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ140" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR140" t="n">
         <v>1.2</v>
@@ -31652,7 +31652,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ143" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR143" t="n">
         <v>1.62</v>
@@ -31870,7 +31870,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR144" t="n">
         <v>1.02</v>
@@ -32960,7 +32960,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR149" t="n">
         <v>1.61</v>
@@ -33829,7 +33829,7 @@
         <v>1</v>
       </c>
       <c r="AP153" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.85</v>
@@ -34050,7 +34050,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR154" t="n">
         <v>1.57</v>
@@ -35355,7 +35355,7 @@
         <v>1</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.92</v>
@@ -35576,7 +35576,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ161" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR161" t="n">
         <v>1.35</v>
@@ -36012,7 +36012,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR163" t="n">
         <v>1.43</v>
@@ -36445,7 +36445,7 @@
         <v>0.75</v>
       </c>
       <c r="AP165" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.08</v>
@@ -36663,7 +36663,7 @@
         <v>0.57</v>
       </c>
       <c r="AP166" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.62</v>
@@ -38407,7 +38407,7 @@
         <v>0.38</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.6899999999999999</v>
@@ -38625,7 +38625,7 @@
         <v>0.88</v>
       </c>
       <c r="AP175" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.92</v>
@@ -39718,7 +39718,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR180" t="n">
         <v>1.23</v>
@@ -41462,7 +41462,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR188" t="n">
         <v>1.76</v>
@@ -41677,7 +41677,7 @@
         <v>1.75</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.23</v>
@@ -42116,7 +42116,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR191" t="n">
         <v>1.49</v>
@@ -42767,7 +42767,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.46</v>
@@ -43639,7 +43639,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.85</v>
@@ -44293,7 +44293,7 @@
         <v>0.44</v>
       </c>
       <c r="AP201" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.33</v>
@@ -45168,7 +45168,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ205" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR205" t="n">
         <v>1.79</v>
@@ -45386,7 +45386,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR206" t="n">
         <v>1.92</v>
@@ -46694,7 +46694,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR212" t="n">
         <v>1.13</v>
@@ -46909,7 +46909,7 @@
         <v>1.78</v>
       </c>
       <c r="AP213" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ213" t="n">
         <v>1.54</v>
@@ -47127,7 +47127,7 @@
         <v>1.3</v>
       </c>
       <c r="AP214" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.31</v>
@@ -48653,7 +48653,7 @@
         <v>0.45</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ221" t="n">
         <v>0.64</v>
@@ -48874,7 +48874,7 @@
         <v>3</v>
       </c>
       <c r="AQ222" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR222" t="n">
         <v>2.25</v>
@@ -49528,7 +49528,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR225" t="n">
         <v>1.38</v>
@@ -50182,7 +50182,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ228" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR228" t="n">
         <v>1.47</v>
@@ -52141,7 +52141,7 @@
         <v>0.55</v>
       </c>
       <c r="AP237" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ237" t="n">
         <v>0.6899999999999999</v>
@@ -52795,7 +52795,7 @@
         <v>1.55</v>
       </c>
       <c r="AP240" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ240" t="n">
         <v>1.54</v>
@@ -53667,10 +53667,10 @@
         <v>2.25</v>
       </c>
       <c r="AP244" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ244" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR244" t="n">
         <v>1.49</v>
@@ -54539,10 +54539,10 @@
         <v>0.42</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ248" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AR248" t="n">
         <v>1.36</v>
@@ -54978,7 +54978,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR250" t="n">
         <v>1.44</v>
@@ -55193,7 +55193,7 @@
         <v>0.67</v>
       </c>
       <c r="AP251" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ251" t="n">
         <v>0.62</v>
@@ -57452,6 +57452,660 @@
       </c>
       <c r="BP261" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>8200624</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>46087.70833333334</v>
+      </c>
+      <c r="F262" t="n">
+        <v>27</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" t="n">
+        <v>2</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="n">
+        <v>2</v>
+      </c>
+      <c r="N262" t="n">
+        <v>3</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>['11', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S262" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T262" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V262" t="n">
+        <v>3</v>
+      </c>
+      <c r="W262" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X262" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ262" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU262" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX262" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY262" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA262" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB262" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC262" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD262" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE262" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF262" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BG262" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH262" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI262" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ262" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BK262" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BL262" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM262" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN262" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO262" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP262" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>8200761</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F263" t="n">
+        <v>27</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>1</v>
+      </c>
+      <c r="K263" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" t="n">
+        <v>2</v>
+      </c>
+      <c r="M263" t="n">
+        <v>2</v>
+      </c>
+      <c r="N263" t="n">
+        <v>4</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>['89', '90+4']</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>['35', '61']</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R263" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S263" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T263" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V263" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="W263" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X263" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ263" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU263" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY263" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA263" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC263" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE263" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF263" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG263" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH263" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI263" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO263" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP263" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>8200739</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>46088.51041666666</v>
+      </c>
+      <c r="F264" t="n">
+        <v>27</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" t="n">
+        <v>1</v>
+      </c>
+      <c r="N264" t="n">
+        <v>2</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R264" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S264" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T264" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U264" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V264" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W264" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X264" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ264" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT264" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU264" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX264" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY264" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA264" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB264" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC264" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BE264" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF264" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG264" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH264" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="BI264" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ264" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK264" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL264" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM264" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN264" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO264" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP264" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Spain La Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP264"/>
+  <dimension ref="A1:BP266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.15</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.33</v>
@@ -3748,7 +3748,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.85</v>
@@ -6146,7 +6146,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>0.79</v>
@@ -7454,7 +7454,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.62</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.54</v>
@@ -9852,7 +9852,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR43" t="n">
         <v>1.29</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.07</v>
@@ -13119,7 +13119,7 @@
         <v>1</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.85</v>
@@ -13776,7 +13776,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR61" t="n">
         <v>0.82</v>
@@ -14427,7 +14427,7 @@
         <v>3</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ64" t="n">
         <v>2.14</v>
@@ -15520,7 +15520,7 @@
         <v>3</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR69" t="n">
         <v>2.26</v>
@@ -16825,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.43</v>
@@ -17482,7 +17482,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR78" t="n">
         <v>1.38</v>
@@ -19223,7 +19223,7 @@
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.64</v>
@@ -19662,7 +19662,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR88" t="n">
         <v>1.73</v>
@@ -21185,7 +21185,7 @@
         <v>1.2</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.31</v>
@@ -21842,7 +21842,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR98" t="n">
         <v>2.25</v>
@@ -23147,7 +23147,7 @@
         <v>1.8</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.15</v>
@@ -24894,7 +24894,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR112" t="n">
         <v>1.61</v>
@@ -25545,7 +25545,7 @@
         <v>1.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.85</v>
@@ -25981,7 +25981,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.46</v>
@@ -26856,7 +26856,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR121" t="n">
         <v>1.51</v>
@@ -27728,7 +27728,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR125" t="n">
         <v>1.42</v>
@@ -30123,7 +30123,7 @@
         <v>0.67</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.46</v>
@@ -31649,7 +31649,7 @@
         <v>1.88</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ143" t="n">
         <v>2.14</v>
@@ -32306,7 +32306,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR146" t="n">
         <v>1.33</v>
@@ -32524,7 +32524,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR147" t="n">
         <v>1.77</v>
@@ -32739,7 +32739,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.31</v>
@@ -34265,7 +34265,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.6899999999999999</v>
@@ -36448,7 +36448,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR165" t="n">
         <v>1.13</v>
@@ -37320,7 +37320,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR169" t="n">
         <v>1.9</v>
@@ -37971,7 +37971,7 @@
         <v>1.57</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.23</v>
@@ -39064,7 +39064,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR177" t="n">
         <v>1.48</v>
@@ -40372,7 +40372,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR183" t="n">
         <v>1.14</v>
@@ -43421,7 +43421,7 @@
         <v>0.44</v>
       </c>
       <c r="AP197" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.62</v>
@@ -43860,7 +43860,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR199" t="n">
         <v>1.62</v>
@@ -45383,7 +45383,7 @@
         <v>0.5</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.43</v>
@@ -47348,7 +47348,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR215" t="n">
         <v>1.61</v>
@@ -48217,10 +48217,10 @@
         <v>1</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR219" t="n">
         <v>1.61</v>
@@ -49743,7 +49743,7 @@
         <v>1</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.85</v>
@@ -49961,7 +49961,7 @@
         <v>1.18</v>
       </c>
       <c r="AP227" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ227" t="n">
         <v>1.46</v>
@@ -51490,7 +51490,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR234" t="n">
         <v>2.36</v>
@@ -52580,7 +52580,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR239" t="n">
         <v>1.2</v>
@@ -53013,7 +53013,7 @@
         <v>0.36</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ241" t="n">
         <v>0.33</v>
@@ -53885,7 +53885,7 @@
         <v>1.36</v>
       </c>
       <c r="AP245" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ245" t="n">
         <v>1.23</v>
@@ -55850,7 +55850,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ254" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR254" t="n">
         <v>1.31</v>
@@ -58106,6 +58106,442 @@
       </c>
       <c r="BP264" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>8200451</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>46088.60416666666</v>
+      </c>
+      <c r="F265" t="n">
+        <v>27</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" t="n">
+        <v>2</v>
+      </c>
+      <c r="L265" t="n">
+        <v>3</v>
+      </c>
+      <c r="M265" t="n">
+        <v>2</v>
+      </c>
+      <c r="N265" t="n">
+        <v>5</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>['5', '67', '81']</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>['9', '68']</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S265" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U265" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V265" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X265" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE265" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG265" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH265" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BI265" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM265" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN265" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO265" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP265" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>8200623</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>46088.70833333334</v>
+      </c>
+      <c r="F266" t="n">
+        <v>27</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>1</v>
+      </c>
+      <c r="N266" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R266" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S266" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U266" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="V266" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X266" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BI266" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
